--- a/output/pdf_financials_xlsx/CANX.xlsx
+++ b/output/pdf_financials_xlsx/CANX.xlsx
@@ -6547,55 +6547,35 @@
       <c r="C107" s="3" t="n">
         <v>2.829</v>
       </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D107" s="3" t="n">
+        <v>1.919197</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>1.983697</v>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>1.983697</v>
+      </c>
+      <c r="G107" s="3" t="n">
+        <v>2.054488</v>
+      </c>
+      <c r="H107" s="3" t="n">
+        <v>2.067399</v>
+      </c>
+      <c r="I107" s="3" t="n">
+        <v>2.109028</v>
+      </c>
+      <c r="J107" s="3" t="n">
+        <v>2.225314</v>
+      </c>
+      <c r="K107" s="3" t="n">
+        <v>2.260775</v>
+      </c>
+      <c r="L107" s="3" t="n">
+        <v>2.271069</v>
+      </c>
+      <c r="M107" s="3" t="n">
+        <v>2.483928</v>
       </c>
     </row>
     <row r="108">
@@ -9545,7 +9525,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CANX.xlsx
+++ b/output/pdf_financials_xlsx/CANX.xlsx
@@ -534,11 +534,15 @@
           <t>Interest Income</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>0.002</v>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
@@ -1341,10 +1345,10 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0</v>
+        <v>0.055</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
@@ -2122,10 +2126,10 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>-1.376</v>
+        <v>-1.431</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>-5.218</v>
+        <v>-5.22</v>
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
@@ -2216,10 +2220,10 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>-1.376</v>
+        <v>-1.431</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>-5.218</v>
+        <v>-5.22</v>
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
@@ -2263,10 +2267,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>-8.18365647674557</v>
+        <v>-8.510764838824789</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>-57.60017661993597</v>
+        <v>-57.62225411193288</v>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
@@ -2820,65 +2824,41 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0.188331</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>0.24275</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>0.134349</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>0.448978</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>1.198099</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>1.458563</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>0.695912</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>0.158093</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>0.663907</v>
       </c>
     </row>
     <row r="47">
@@ -2936,47 +2916,41 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>0.016</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.4535</v>
+        <v>0.641831</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.178163</v>
+        <v>0.468093</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.24595</v>
+        <v>0.4887</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.353715</v>
+        <v>0.488064</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.551271</v>
+        <v>1.000249</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.619686</v>
+        <v>1.817785</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.309842</v>
+        <v>1.768405</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.08984200000000001</v>
+        <v>0.785754</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.031035</v>
-      </c>
-      <c r="M48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.189128</v>
+      </c>
+      <c r="M48" s="3" t="n">
+        <v>0.663907</v>
       </c>
     </row>
     <row r="49">
@@ -3675,40 +3649,40 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>0.777</v>
+        <v>0.761</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>0.251</v>
+        <v>0.235</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>0.197122</v>
+        <v>0.008791</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>0.324123</v>
+        <v>0.034193</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.2827</v>
+        <v>0.03995</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.204394</v>
+        <v>0.070045</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>0.490239</v>
+        <v>0.041261</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>1.268516</v>
+        <v>0.07041699999999999</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>1.494772</v>
+        <v>0.036209</v>
       </c>
       <c r="K60" s="3" t="n">
-        <v>0.732019</v>
+        <v>0.036107</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>0.170879</v>
+        <v>0.012786</v>
       </c>
       <c r="M60" s="3" t="n">
-        <v>0.738148</v>
+        <v>0.074241</v>
       </c>
     </row>
     <row r="61">
@@ -8615,7 +8589,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10813,7 +10787,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -13531,7 +13505,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
@@ -22325,7 +22299,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E189" s="5" t="n">

--- a/output/pdf_financials_xlsx/CANX.xlsx
+++ b/output/pdf_financials_xlsx/CANX.xlsx
@@ -4777,55 +4777,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D79" s="3" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>0.020327</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>0.026934</v>
+      </c>
+      <c r="H79" s="3" t="n">
+        <v>0.0255</v>
+      </c>
+      <c r="I79" s="3" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J79" s="3" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="K79" s="3" t="n">
+        <v>0.039125</v>
+      </c>
+      <c r="L79" s="3" t="n">
+        <v>0.0409</v>
+      </c>
+      <c r="M79" s="3" t="n">
+        <v>0.0468</v>
       </c>
     </row>
     <row r="80">
